--- a/data/vip2023.xlsx
+++ b/data/vip2023.xlsx
@@ -1,29 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabelhaas/Documents/Coding/aytogermany/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D22840C-4E09-D04B-9CBF-07CDE9D157FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="240" yWindow="680" windowWidth="32720" windowHeight="17160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Candidates" sheetId="1" r:id="rId1"/>
-    <sheet name="Nights" sheetId="2" r:id="rId2"/>
-    <sheet name="Matchboxes" sheetId="3" r:id="rId3"/>
-    <sheet name="Solution" sheetId="4" r:id="rId4"/>
+    <sheet sheetId="1" name="Candidates" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Nights" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Matchboxes" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Solution" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="32">
   <si>
     <t>left</t>
   </si>
@@ -103,28 +94,51 @@
     <t>episode</t>
   </si>
   <si>
+    <t>Frau</t>
+  </si>
+  <si>
+    <t>Mann</t>
+  </si>
+  <si>
     <t>result</t>
+  </si>
+  <si>
+    <t>before_night</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF2C3E50"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF2C3E50"/>
+      <sz val="12"/>
+      <name val="Times"/>
     </font>
   </fonts>
   <fills count="3">
@@ -137,7 +151,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC5C6C7"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -153,17 +166,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -250,6 +269,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -284,6 +304,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -318,20 +339,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -453,20 +470,60 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="10.6640625" customWidth="1"/>
+    <col min="1" max="3" width="10.714285714285714" customWidth="1"/>
+    <col min="4" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -488,7 +545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -496,7 +553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -504,7 +561,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -512,7 +569,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -520,7 +577,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -528,7 +585,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -536,7 +593,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -544,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -552,7 +609,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -560,25 +617,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="11" width="10.6640625" customWidth="1"/>
+    <col min="1" max="11" width="10.714285714285714" customWidth="1"/>
+    <col min="12" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -613,7 +672,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -648,7 +707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -683,7 +742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -718,7 +777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -753,7 +812,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -788,7 +847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -823,7 +882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -858,7 +917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -893,7 +952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -928,7 +987,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -965,32 +1024,37 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="4" width="10.714285714285714" customWidth="1"/>
+    <col min="5" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1000,11 +1064,14 @@
       <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1014,11 +1081,14 @@
       <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1028,11 +1098,14 @@
       <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1042,11 +1115,14 @@
       <c r="C5" t="s">
         <v>4</v>
       </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1056,11 +1132,14 @@
       <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1070,11 +1149,14 @@
       <c r="C7" t="s">
         <v>7</v>
       </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1084,11 +1166,14 @@
       <c r="C8" t="s">
         <v>5</v>
       </c>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1098,11 +1183,14 @@
       <c r="C9" t="s">
         <v>9</v>
       </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1112,21 +1200,31 @@
       <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1134,7 +1232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -1142,7 +1240,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1150,7 +1248,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1158,7 +1256,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1166,7 +1264,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1174,7 +1272,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1182,7 +1280,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1190,7 +1288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1198,7 +1296,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1206,7 +1304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1214,7 +1312,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1223,6 +1321,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>